--- a/data/trans_orig/P33B_R5-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R5-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7978</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12499</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>18491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>306606</t>
+          <t>314324</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301441</t>
+          <t>309157</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309673</t>
+          <t>316805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>282225</t>
+          <t>308083</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277638</t>
+          <t>303471</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285355</t>
+          <t>311477</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>588830</t>
+          <t>622407</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582485</t>
+          <t>616415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>593609</t>
+          <t>626816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23413</t>
+          <t>23856</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35412</t>
+          <t>35552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63799</t>
+          <t>66770</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52075</t>
+          <t>54815</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76832</t>
+          <t>80312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>87211</t>
+          <t>90625</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71437</t>
+          <t>75332</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104917</t>
+          <t>108425</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>493980</t>
+          <t>505804</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481981</t>
+          <t>494108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502348</t>
+          <t>514931</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>450604</t>
+          <t>479128</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>437571</t>
+          <t>465586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>462328</t>
+          <t>491083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>944585</t>
+          <t>984933</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>926879</t>
+          <t>967133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>960359</t>
+          <t>1000226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514403</t>
+          <t>545898</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514403</t>
+          <t>545898</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514403</t>
+          <t>545898</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031796</t>
+          <t>1075558</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031796</t>
+          <t>1075558</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031796</t>
+          <t>1075558</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25635</t>
+          <t>27117</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>35681</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>32703</t>
+          <t>34153</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24820</t>
+          <t>25819</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43270</t>
+          <t>42678</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>308982</t>
+          <t>308957</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303423</t>
+          <t>303242</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312353</t>
+          <t>312108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>323493</t>
+          <t>329264</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>316028</t>
+          <t>320700</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330533</t>
+          <t>336497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>632475</t>
+          <t>638222</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621908</t>
+          <t>629697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640358</t>
+          <t>646556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>25300</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14608</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32024</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>39588</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22926</t>
+          <t>31113</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49994</t>
+          <t>49530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>58614</t>
+          <t>64888</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40900</t>
+          <t>53300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73491</t>
+          <t>80555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>290473</t>
+          <t>347845</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>280533</t>
+          <t>334927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297949</t>
+          <t>356031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>439189</t>
+          <t>382373</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>425724</t>
+          <t>372431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>452792</t>
+          <t>390848</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>729660</t>
+          <t>730219</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>714783</t>
+          <t>714552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>747374</t>
+          <t>741807</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>22951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25253</t>
+          <t>26830</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19159</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32846</t>
+          <t>33989</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>169658</t>
+          <t>196150</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164294</t>
+          <t>190134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173433</t>
+          <t>199961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>192106</t>
+          <t>209508</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186771</t>
+          <t>203872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196211</t>
+          <t>214057</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>361763</t>
+          <t>405658</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354170</t>
+          <t>398499</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367857</t>
+          <t>412137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23509</t>
+          <t>23466</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42768</t>
+          <t>43803</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34363</t>
+          <t>35729</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52057</t>
+          <t>52674</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>59314</t>
+          <t>60052</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48928</t>
+          <t>50932</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70755</t>
+          <t>70012</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>253090</t>
+          <t>254458</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246127</t>
+          <t>247241</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257993</t>
+          <t>259461</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>214288</t>
+          <t>219947</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>204999</t>
+          <t>211076</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222693</t>
+          <t>228021</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>467378</t>
+          <t>474405</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>455937</t>
+          <t>464445</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>477764</t>
+          <t>483525</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,47%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>40611</t>
+          <t>44513</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27806</t>
+          <t>31455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58169</t>
+          <t>65178</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>72952</t>
+          <t>89722</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>73170</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>103607</t>
+          <t>108741</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>113562</t>
+          <t>134235</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69819</t>
+          <t>114679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>142712</t>
+          <t>159322</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>582639</t>
+          <t>674092</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>565081</t>
+          <t>653427</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>595444</t>
+          <t>687150</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>775723</t>
+          <t>681666</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>745068</t>
+          <t>662647</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>813416</t>
+          <t>698218</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1358362</t>
+          <t>1355758</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1329212</t>
+          <t>1330671</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1402105</t>
+          <t>1375314</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848675</t>
+          <t>771388</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848675</t>
+          <t>771388</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848675</t>
+          <t>771388</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1471924</t>
+          <t>1489993</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1471924</t>
+          <t>1489993</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1471924</t>
+          <t>1489993</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>95273</t>
+          <t>106588</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42330</t>
+          <t>89287</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137329</t>
+          <t>125060</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>162369</t>
+          <t>181944</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>145038</t>
+          <t>161621</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>183543</t>
+          <t>200681</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>257642</t>
+          <t>288531</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160498</t>
+          <t>263204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>314695</t>
+          <t>317919</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>833447</t>
+          <t>691484</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>791391</t>
+          <t>673012</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>886390</t>
+          <t>708785</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>553023</t>
+          <t>648665</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>531849</t>
+          <t>629928</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>570354</t>
+          <t>668988</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1386470</t>
+          <t>1340150</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1329417</t>
+          <t>1310762</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1483614</t>
+          <t>1365477</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>83,84%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>218916</t>
+          <t>237576</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>168381</t>
+          <t>208439</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>253439</t>
+          <t>268293</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>427630</t>
+          <t>474236</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>348865</t>
+          <t>441591</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>472318</t>
+          <t>507802</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>646547</t>
+          <t>711812</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>557091</t>
+          <t>668340</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>705134</t>
+          <t>756581</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3238875</t>
+          <t>3293117</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3204352</t>
+          <t>3262400</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3289410</t>
+          <t>3322254</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3230649</t>
+          <t>3258637</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3185961</t>
+          <t>3225071</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3309414</t>
+          <t>3291282</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6469523</t>
+          <t>6551753</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6410936</t>
+          <t>6506984</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6558979</t>
+          <t>6595225</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
